--- a/data/trans_bre/P1001-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1001-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 7,61</t>
+          <t>-3,9; 7,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 17,48</t>
+          <t>5,28; 17,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 16,12</t>
+          <t>1,68; 16,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,54</t>
+          <t>-1,47; 3,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 99,43</t>
+          <t>-30,26; 101,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,95; 232,72</t>
+          <t>38,82; 219,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,27; 124,88</t>
+          <t>8,59; 122,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 262,41</t>
+          <t>-43,31; 245,59</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 10,81</t>
+          <t>2,71; 10,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 11,35</t>
+          <t>2,85; 11,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,34</t>
+          <t>3,75; 9,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 6,5</t>
+          <t>-0,47; 6,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,54; 168,59</t>
+          <t>26,37; 185,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,35; 188,84</t>
+          <t>26,85; 196,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,51; 516,24</t>
+          <t>86,09; 576,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 109,68</t>
+          <t>-6,21; 133,75</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,07</t>
+          <t>-1,4; 4,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 10,15</t>
+          <t>1,25; 9,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,3</t>
+          <t>0,7; 6,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 6,3</t>
+          <t>0,07; 6,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,95; 339,05</t>
+          <t>-43,11; 308,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,93; 295,55</t>
+          <t>10,56; 258,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 532,67</t>
+          <t>11,54; 604,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 165,78</t>
+          <t>-1,11; 182,98</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 8,81</t>
+          <t>2,07; 8,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 20,84</t>
+          <t>11,18; 20,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 16,9</t>
+          <t>6,59; 16,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 7,41</t>
+          <t>-1,77; 7,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,21; 572,91</t>
+          <t>46,56; 600,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>149,63; 544,74</t>
+          <t>144,58; 591,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,19; 246,4</t>
+          <t>55,25; 233,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 172,07</t>
+          <t>-21,79; 209,45</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 5,71</t>
+          <t>-4,52; 5,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 20,12</t>
+          <t>7,53; 19,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 7,71</t>
+          <t>-1,51; 7,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,7</t>
+          <t>3,2; 9,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 130,32</t>
+          <t>-50,3; 123,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,53; 698,28</t>
+          <t>92,93; 655,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,81; 271,79</t>
+          <t>-26,74; 308,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>54,83; 571,92</t>
+          <t>58,21; 555,51</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 6,23</t>
+          <t>0,7; 6,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 8,29</t>
+          <t>-1,87; 8,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 12,24</t>
+          <t>2,08; 12,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 6,3</t>
+          <t>-0,66; 5,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 1108,7</t>
+          <t>-20,52; 1179,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 152,76</t>
+          <t>-18,29; 135,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 222,97</t>
+          <t>19,76; 241,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 157,76</t>
+          <t>-11,41; 154,05</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,74</t>
+          <t>1,7; 7,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,95</t>
+          <t>0,31; 6,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,97</t>
+          <t>2,87; 9,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 7,89</t>
+          <t>-4,59; 7,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,45; 180,2</t>
+          <t>22,89; 173,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 156,77</t>
+          <t>3,18; 158,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,95; 200,02</t>
+          <t>36,41; 204,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-43,76; 99,2</t>
+          <t>-40,39; 96,39</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,34</t>
+          <t>-1,28; 4,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,8</t>
+          <t>3,92; 10,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,35</t>
+          <t>1,59; 6,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,62; 16,18</t>
+          <t>8,85; 15,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 66,19</t>
+          <t>-14,02; 67,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,33; 145,45</t>
+          <t>33,56; 147,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,36; 214,01</t>
+          <t>30,21; 205,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>135,41; 708,5</t>
+          <t>146,67; 695,11</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,69</t>
+          <t>2,14; 4,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,08</t>
+          <t>6,2; 9,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,52</t>
+          <t>4,75; 7,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,69</t>
+          <t>3,01; 6,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,8; 85,8</t>
+          <t>31,87; 86,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75,82; 139,57</t>
+          <t>79,9; 142,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,81; 138,51</t>
+          <t>70,94; 138,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49,35; 139,21</t>
+          <t>48,89; 143,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1001-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1001-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>56,19%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 7,5</t>
+          <t>-3,91; 7,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 17,28</t>
+          <t>5,18; 17,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 16,12</t>
+          <t>2,94; 16,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,51</t>
+          <t>-1,15; 3,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 101,51</t>
+          <t>-29,42; 99,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,82; 219,25</t>
+          <t>38,77; 227,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 122,78</t>
+          <t>14,41; 135,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,31; 245,59</t>
+          <t>-34,52; 265,46</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,26</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 10,91</t>
+          <t>3,08; 10,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,51</t>
+          <t>2,86; 11,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 9,88</t>
+          <t>3,46; 9,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 6,81</t>
+          <t>-0,82; 6,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,37; 185,69</t>
+          <t>27,38; 162,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,85; 196,42</t>
+          <t>24,76; 200,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,09; 576,52</t>
+          <t>77,91; 523,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 133,75</t>
+          <t>-9,0; 115,26</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>3,13</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,01</t>
+          <t>-1,41; 3,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 9,81</t>
+          <t>1,61; 10,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,79</t>
+          <t>0,59; 6,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,51</t>
+          <t>-0,41; 6,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,11; 308,61</t>
+          <t>-48,9; 307,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 258,94</t>
+          <t>12,12; 294,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,54; 604,05</t>
+          <t>3,05; 637,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 182,98</t>
+          <t>-6,2; 170,56</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>5,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>104,32%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,57</t>
+          <t>1,83; 8,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,18; 20,64</t>
+          <t>10,91; 20,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,59; 16,67</t>
+          <t>6,81; 17,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 7,95</t>
+          <t>1,89; 10,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,56; 600,7</t>
+          <t>32,11; 579,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>144,58; 591,08</t>
+          <t>136,83; 526,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,25; 233,49</t>
+          <t>55,37; 243,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 209,45</t>
+          <t>21,52; 272,68</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,57</t>
+          <t>6,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>212,56%</t>
+          <t>218,89%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 5,49</t>
+          <t>-4,1; 5,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 19,69</t>
+          <t>7,28; 19,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 7,59</t>
+          <t>-1,63; 7,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 9,88</t>
+          <t>3,07; 9,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,3; 123,55</t>
+          <t>-49,49; 135,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,93; 655,91</t>
+          <t>99,5; 716,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 308,77</t>
+          <t>-29,42; 246,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,21; 555,51</t>
+          <t>68,39; 567,42</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,42</t>
+          <t>0,5; 6,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 8,13</t>
+          <t>-2,0; 7,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 12,23</t>
+          <t>0,96; 12,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,9</t>
+          <t>-0,43; 6,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 1179,8</t>
+          <t>9,13; 1494,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 135,71</t>
+          <t>-19,41; 136,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,76; 241,65</t>
+          <t>7,37; 247,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 154,05</t>
+          <t>-8,72; 165,03</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>6,93</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,67</t>
+          <t>2,0; 7,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,13</t>
+          <t>0,61; 6,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 9,75</t>
+          <t>3,24; 9,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 7,78</t>
+          <t>3,28; 10,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,89; 173,34</t>
+          <t>26,41; 182,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 158,06</t>
+          <t>6,02; 160,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,41; 204,58</t>
+          <t>37,45; 193,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 96,39</t>
+          <t>32,12; 153,83</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11,82</t>
+          <t>9,7</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>272,1%</t>
+          <t>167,67%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,5</t>
+          <t>-1,09; 4,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 10,94</t>
+          <t>4,08; 10,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,42</t>
+          <t>1,52; 6,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,85; 15,71</t>
+          <t>7,19; 12,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 67,36</t>
+          <t>-12,04; 71,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,56; 147,55</t>
+          <t>37,57; 147,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,21; 205,71</t>
+          <t>27,6; 206,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>146,67; 695,11</t>
+          <t>96,25; 265,72</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,7</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,75</t>
+          <t>2,08; 4,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,27</t>
+          <t>6,11; 8,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,49</t>
+          <t>4,64; 7,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,69</t>
+          <t>4,5; 6,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,87; 86,4</t>
+          <t>31,78; 87,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>79,9; 142,72</t>
+          <t>78,56; 141,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>70,94; 138,12</t>
+          <t>69,69; 139,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>48,89; 143,9</t>
+          <t>65,56; 125,88</t>
         </is>
       </c>
     </row>
